--- a/data/sars/alaska/tables/Alaska_1999_Appendix2.xlsx
+++ b/data/sars/alaska/tables/Alaska_1999_Appendix2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2F2986-7F3C-8E49-9875-948CBB02CBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6700" yWindow="8280" windowWidth="28040" windowHeight="17440" xr2:uid="{053BAA84-9D2C-244E-B14D-348ECE1A52BF}"/>
+    <workbookView xWindow="6680" yWindow="4960" windowWidth="28040" windowHeight="17440" xr2:uid="{053BAA84-9D2C-244E-B14D-348ECE1A52BF}"/>
   </bookViews>
   <sheets>
     <sheet name="tabula-Alaska_1999_Appendix2" sheetId="1" r:id="rId1"/>
